--- a/eval_results_pid.xlsx
+++ b/eval_results_pid.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="D2" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="E2" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="F2" t="n">
-        <v>0.079</v>
+        <v>0.096</v>
       </c>
       <c r="G2" t="n">
-        <v>0.106</v>
+        <v>0.125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.146</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -512,28 +512,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.001763492063492064</v>
+        <v>0.002878968253968254</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005897619047619049</v>
+        <v>0.009988095238095239</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009034920634920634</v>
+        <v>0.01403611111111111</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01402142857142856</v>
+        <v>0.02848888888888887</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02144365079365078</v>
+        <v>0.03790595238095238</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03048412698412697</v>
+        <v>0.06009960317460324</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01259216382193173</v>
+        <v>0.01405654849244573</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01221260054110822</v>
+        <v>0.01431983530475147</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01269416907414274</v>
+        <v>0.01955866346204493</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01573423036293674</v>
+        <v>0.02323204389518585</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01917535472884331</v>
+        <v>0.03017729985741122</v>
       </c>
     </row>
     <row r="5">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="D5" t="n">
-        <v>0.051</v>
+        <v>0.044</v>
       </c>
       <c r="E5" t="n">
-        <v>0.067</v>
+        <v>0.045</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.115</v>
+        <v>0.053</v>
       </c>
       <c r="H5" t="n">
-        <v>0.146</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="6">
@@ -602,22 +602,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.002411111111111111</v>
+        <v>0.004084126984126985</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006695238095238093</v>
+        <v>0.005132539682539684</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009074999999999995</v>
+        <v>0.005243650793650795</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01504920634920633</v>
+        <v>0.006533730158730156</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01744761904761903</v>
+        <v>0.007205952380952378</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02179325396825395</v>
+        <v>0.008594841269841265</v>
       </c>
     </row>
     <row r="7">
@@ -632,22 +632,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0185699021643186</v>
+        <v>0.01889403413681923</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01628950568083011</v>
+        <v>0.0138012888849828</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01558070180100097</v>
+        <v>0.01053400192630264</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01690077614621596</v>
+        <v>0.01090257611389511</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01895363421332586</v>
+        <v>0.01152466054606724</v>
       </c>
     </row>
   </sheetData>
